--- a/wikischema/File/Cyclic_Voltammetry_Template.xlsx
+++ b/wikischema/File/Cyclic_Voltammetry_Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kai\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{86998CE1-D100-4F02-B981-DC3999127B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBC4F5EC-0703-44F3-870F-C67A0C75E9D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,42 +20,69 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
-  <si>
-    <t>Analyte</t>
-  </si>
-  <si>
-    <t>Analyte_data</t>
-  </si>
-  <si>
-    <t>Analyte concentration</t>
-  </si>
-  <si>
-    <t>Reduction potential</t>
-  </si>
-  <si>
-    <t>Reduction potential_data</t>
-  </si>
-  <si>
-    <t>Solvent A</t>
-  </si>
-  <si>
-    <t>Solvent A_data</t>
-  </si>
-  <si>
-    <t>Solvent volume</t>
-  </si>
-  <si>
-    <t>Electrolyte</t>
-  </si>
-  <si>
-    <t>Electrolyte concentration</t>
-  </si>
-  <si>
-    <t>Internal reference compound</t>
-  </si>
-  <si>
-    <t>Scan rate</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+  <si>
+    <t>Analyte_inchikey</t>
+  </si>
+  <si>
+    <t>Analyte_molfile</t>
+  </si>
+  <si>
+    <t>Analyte concentration [mM]</t>
+  </si>
+  <si>
+    <t>Redox potential</t>
+  </si>
+  <si>
+    <t>E0 [V]</t>
+  </si>
+  <si>
+    <t>Ered1 [V]</t>
+  </si>
+  <si>
+    <t>Ered2 [V]</t>
+  </si>
+  <si>
+    <t>Ered3 [V]</t>
+  </si>
+  <si>
+    <t>Eox1 [V]</t>
+  </si>
+  <si>
+    <t>Eox2 [V]</t>
+  </si>
+  <si>
+    <t>Eox3 [V]</t>
+  </si>
+  <si>
+    <t>Solvent A_inchikey</t>
+  </si>
+  <si>
+    <t>Solvent A_molfile</t>
+  </si>
+  <si>
+    <t>Solvent volume [ml]</t>
+  </si>
+  <si>
+    <t>Electrolyte_inchikey</t>
+  </si>
+  <si>
+    <t>Electrolyte_molfile</t>
+  </si>
+  <si>
+    <t>Electrolyte purity [%]</t>
+  </si>
+  <si>
+    <t>Electrolyte concentration [M]</t>
+  </si>
+  <si>
+    <t>Internal reference compound_inchikey</t>
+  </si>
+  <si>
+    <t>Internal reference compound_molfile</t>
+  </si>
+  <si>
+    <t>Scan rate [mV/s]</t>
   </si>
   <si>
     <t>Scan number</t>
@@ -70,7 +97,7 @@
     <t>Gas</t>
   </si>
   <si>
-    <t>Temperature</t>
+    <t>TemperatureP [°C]</t>
   </si>
   <si>
     <t>Condition</t>
@@ -79,7 +106,7 @@
     <t>Working electrode</t>
   </si>
   <si>
-    <t>Working electrode surface area</t>
+    <t>Working electrode surface area [mm²]</t>
   </si>
   <si>
     <t>Counter electrode</t>
@@ -441,13 +468,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="25" max="25" width="22.5703125" customWidth="1"/>
+    <col min="3" max="3" width="33.28515625" customWidth="1"/>
+    <col min="4" max="4" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -522,6 +550,33 @@
       </c>
       <c r="Y1" s="1" t="s">
         <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
